--- a/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-bundle-urgencia.xlsx
+++ b/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-bundle-urgencia.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5208" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5208" uniqueCount="392">
   <si>
     <t>Property</t>
   </si>
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia/StructureDefinition/bundle-urgencia</t>
+    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/StructureDefinition/bundle-urgencia</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:36:45-03:00</t>
+    <t>2026-09-24T11:47:41-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -262,7 +262,7 @@
 </t>
   </si>
   <si>
-    <t>Contains a collection of resources</t>
+    <t>Bundle transaction de un evento de urgencia</t>
   </si>
   <si>
     <t>A container for a collection of resources.</t>
@@ -395,16 +395,13 @@
     <t>Bundle.type</t>
   </si>
   <si>
-    <t>document | message | transaction | transaction-response | batch | batch-response | history | searchset | collection</t>
+    <t>transaction</t>
   </si>
   <si>
     <t>Indicates the purpose of this bundle - how it is intended to be used.</t>
   </si>
   <si>
     <t>It's possible to use a bundle for other purposes (e.g. a document can be accepted as a transaction). This is primarily defined so that there can be specific rules for some of the bundle types.</t>
-  </si>
-  <si>
-    <t>transaction</t>
   </si>
   <si>
     <t>required</t>
@@ -576,7 +573,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Entry in the bundle - will have a resource or information</t>
+    <t>Entrada: recurso más su PUT condicional</t>
   </si>
   <si>
     <t>An entry in a bundle resource - will either contain a resource or information about a resource (transactions and history only).</t>
@@ -633,7 +630,7 @@
 </t>
   </si>
   <si>
-    <t>A resource in the bundle</t>
+    <t>Recurso de la entrada</t>
   </si>
   <si>
     <t>The Resource for the entry. The purpose/meaning of the resource is determined by the Bundle.type.</t>
@@ -699,7 +696,7 @@
     <t>Bundle.entry.request</t>
   </si>
   <si>
-    <t>Additional execution information (transaction/batch/history)</t>
+    <t>Operación: PUT condicional por identificador</t>
   </si>
   <si>
     <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
@@ -721,13 +718,10 @@
     <t>Bundle.entry.request.method</t>
   </si>
   <si>
-    <t>GET | HEAD | POST | PUT | DELETE | PATCH</t>
+    <t>PUT</t>
   </si>
   <si>
     <t>In a transaction or batch, this is the HTTP action to be executed for this entry. In a history bundle, this indicates the HTTP action that occurred.</t>
-  </si>
-  <si>
-    <t>PUT</t>
   </si>
   <si>
     <t>HTTP verbs (in the HTTP command line). See [HTTP rfc](https://tools.ietf.org/html/rfc7231) for details.</t>
@@ -864,6 +858,9 @@
     <t>paciente</t>
   </si>
   <si>
+    <t>Paciente</t>
+  </si>
+  <si>
     <t>Bundle.entry:paciente.id</t>
   </si>
   <si>
@@ -890,7 +887,7 @@
 </t>
   </si>
   <si>
-    <t>Information about an individual or animal receiving health care services</t>
+    <t>Paciente (MINSALPaciente del NID)</t>
   </si>
   <si>
     <t>Demographics and other administrative information about an individual or animal receiving care or other health-related services.</t>
@@ -921,6 +918,9 @@
   </si>
   <si>
     <t>Bundle.entry:paciente.request</t>
+  </si>
+  <si>
+    <t>PUT Patient?identifier=[sistema]|[valor]</t>
   </si>
   <si>
     <t>Bundle.entry:paciente.request.id</t>
@@ -1008,7 +1008,7 @@
 </t>
   </si>
   <si>
-    <t>A grouping of people or organizations with a common purpose</t>
+    <t>Establecimiento (MINSALPrestadorOrganizacional del NID)</t>
   </si>
   <si>
     <t>A formally or informally recognized grouping of people or organizations formed for the purpose of achieving some form of collective action.  Includes companies, institutions, corporations, departments, community groups, healthcare practice groups, payer/insurer, etc.</t>
@@ -1041,6 +1041,9 @@
     <t>Bundle.entry:establecimiento.request</t>
   </si>
   <si>
+    <t>PUT Organization?identifier=[sistema DEIS]|[código]</t>
+  </si>
+  <si>
     <t>Bundle.entry:establecimiento.request.id</t>
   </si>
   <si>
@@ -1099,6 +1102,9 @@
   </si>
   <si>
     <t>profesional</t>
+  </si>
+  <si>
+    <t>Profesional (opcional)</t>
   </si>
   <si>
     <t>Bundle.entry:profesional.id</t>
@@ -1123,7 +1129,7 @@
 </t>
   </si>
   <si>
-    <t>A person with a  formal responsibility in the provisioning of healthcare or related services</t>
+    <t>Profesional (MINSALPrestadorProfesional del NID)</t>
   </si>
   <si>
     <t>A person who is directly or indirectly involved in the provisioning of healthcare.</t>
@@ -1154,6 +1160,9 @@
   </si>
   <si>
     <t>Bundle.entry:profesional.request</t>
+  </si>
+  <si>
+    <t>PUT Practitioner?identifier=[sistema]|[RUN]</t>
   </si>
   <si>
     <t>Bundle.entry:profesional.request.id</t>
@@ -2437,28 +2446,28 @@
         <v>77</v>
       </c>
       <c r="S8" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X8" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="T8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X8" t="s" s="2">
+      <c r="Y8" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="Y8" t="s" s="2">
+      <c r="Z8" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="Z8" t="s" s="2">
-        <v>129</v>
       </c>
       <c r="AA8" t="s" s="2">
         <v>77</v>
@@ -2500,15 +2509,15 @@
         <v>77</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2531,16 +2540,16 @@
         <v>88</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>135</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2590,7 +2599,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2611,18 +2620,18 @@
         <v>77</v>
       </c>
       <c r="AM9" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AN9" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AN9" t="s" s="2">
-        <v>137</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2645,16 +2654,16 @@
         <v>88</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L10" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="M10" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="M10" t="s" s="2">
+      <c r="N10" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2704,7 +2713,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2713,7 +2722,7 @@
         <v>87</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>99</v>
@@ -2733,10 +2742,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2759,16 +2768,16 @@
         <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>145</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="M11" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="M11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>148</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2818,7 +2827,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2847,10 +2856,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2873,13 +2882,13 @@
         <v>77</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2930,25 +2939,25 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH12" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL12" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>77</v>
@@ -2959,14 +2968,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2985,16 +2994,16 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3044,7 +3053,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3056,13 +3065,13 @@
         <v>77</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
@@ -3073,14 +3082,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3099,19 +3108,19 @@
         <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O14" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>77</v>
@@ -3160,7 +3169,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3172,7 +3181,7 @@
         <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>77</v>
@@ -3189,10 +3198,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3215,13 +3224,13 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3272,7 +3281,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>87</v>
@@ -3301,10 +3310,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3330,10 +3339,10 @@
         <v>101</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3384,7 +3393,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>87</v>
@@ -3413,10 +3422,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3424,7 +3433,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>79</v>
@@ -3439,13 +3448,13 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3484,17 +3493,17 @@
         <v>77</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AC17" s="2"/>
       <c r="AD17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3506,7 +3515,7 @@
         <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>77</v>
@@ -3523,10 +3532,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3549,13 +3558,13 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3606,25 +3615,25 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3635,14 +3644,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3661,16 +3670,16 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3720,7 +3729,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3732,13 +3741,13 @@
         <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3749,14 +3758,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3775,19 +3784,19 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O20" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -3836,7 +3845,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3848,7 +3857,7 @@
         <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
@@ -3865,10 +3874,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3894,10 +3903,10 @@
         <v>80</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3948,7 +3957,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3977,10 +3986,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4006,13 +4015,13 @@
         <v>101</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4062,7 +4071,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4091,10 +4100,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4117,13 +4126,13 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4174,7 +4183,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4203,10 +4212,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4229,13 +4238,13 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4286,7 +4295,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4295,7 +4304,7 @@
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>99</v>
@@ -4315,10 +4324,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4341,13 +4350,13 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4398,25 +4407,25 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4427,14 +4436,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4453,16 +4462,16 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4512,7 +4521,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4524,13 +4533,13 @@
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4541,14 +4550,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4567,19 +4576,19 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O27" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4628,7 +4637,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4640,7 +4649,7 @@
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
@@ -4657,10 +4666,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4686,13 +4695,13 @@
         <v>107</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4718,14 +4727,14 @@
         <v>77</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="Z28" t="s" s="2">
-        <v>208</v>
-      </c>
       <c r="AA28" t="s" s="2">
         <v>77</v>
       </c>
@@ -4742,7 +4751,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4771,10 +4780,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4797,16 +4806,16 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4856,7 +4865,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4885,10 +4894,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4911,13 +4920,13 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4968,7 +4977,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4977,7 +4986,7 @@
         <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>99</v>
@@ -4997,10 +5006,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5023,13 +5032,13 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5080,25 +5089,25 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL31" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
@@ -5109,14 +5118,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5135,16 +5144,16 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5194,7 +5203,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5206,13 +5215,13 @@
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -5223,14 +5232,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5249,19 +5258,19 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O33" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5310,7 +5319,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5322,7 +5331,7 @@
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>77</v>
@@ -5339,10 +5348,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5368,10 +5377,10 @@
         <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5383,29 +5392,29 @@
         <v>77</v>
       </c>
       <c r="S34" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="Z34" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="T34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X34" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>226</v>
-      </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
       </c>
@@ -5422,7 +5431,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>87</v>
@@ -5451,10 +5460,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5480,13 +5489,13 @@
         <v>101</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5536,7 +5545,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>87</v>
@@ -5565,10 +5574,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5591,13 +5600,13 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5648,7 +5657,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5677,10 +5686,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5703,13 +5712,13 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5760,7 +5769,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5789,10 +5798,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5815,13 +5824,13 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5872,7 +5881,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5901,10 +5910,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5927,13 +5936,13 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5984,7 +5993,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6013,10 +6022,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6039,13 +6048,13 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6096,7 +6105,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6105,7 +6114,7 @@
         <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>99</v>
@@ -6125,10 +6134,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6151,13 +6160,13 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6208,25 +6217,25 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6237,14 +6246,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6263,16 +6272,16 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6322,7 +6331,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6334,13 +6343,13 @@
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6351,14 +6360,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6377,19 +6386,19 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O43" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6438,7 +6447,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6450,7 +6459,7 @@
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
@@ -6467,10 +6476,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6493,13 +6502,13 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6550,7 +6559,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>87</v>
@@ -6579,10 +6588,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6608,10 +6617,10 @@
         <v>101</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6662,7 +6671,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6691,10 +6700,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6717,16 +6726,16 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6776,7 +6785,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6805,10 +6814,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6831,16 +6840,16 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6890,7 +6899,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6919,10 +6928,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6945,16 +6954,16 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7004,7 +7013,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7033,13 +7042,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>77</v>
@@ -7061,13 +7070,13 @@
         <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7118,7 +7127,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7130,7 +7139,7 @@
         <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
@@ -7147,10 +7156,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7173,13 +7182,13 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7230,25 +7239,25 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -7259,14 +7268,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7285,16 +7294,16 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7344,7 +7353,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7356,13 +7365,13 @@
         <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7373,14 +7382,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7399,19 +7408,19 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O52" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7460,7 +7469,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7472,7 +7481,7 @@
         <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
@@ -7489,10 +7498,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7518,10 +7527,10 @@
         <v>80</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7572,7 +7581,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7601,10 +7610,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7630,13 +7639,13 @@
         <v>101</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7686,7 +7695,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7715,14 +7724,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7741,13 +7750,13 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7798,7 +7807,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7816,10 +7825,10 @@
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>
@@ -7827,10 +7836,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7853,13 +7862,13 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7910,7 +7919,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -7919,7 +7928,7 @@
         <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>99</v>
@@ -7939,10 +7948,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7965,13 +7974,13 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8022,25 +8031,25 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL57" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -8051,14 +8060,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8077,16 +8086,16 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8136,7 +8145,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8148,13 +8157,13 @@
         <v>77</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
@@ -8165,14 +8174,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8191,19 +8200,19 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O59" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8252,7 +8261,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8264,7 +8273,7 @@
         <v>77</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
@@ -8281,10 +8290,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8310,13 +8319,13 @@
         <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8342,14 +8351,14 @@
         <v>77</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Y60" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="Z60" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="Z60" t="s" s="2">
-        <v>208</v>
-      </c>
       <c r="AA60" t="s" s="2">
         <v>77</v>
       </c>
@@ -8366,7 +8375,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8395,10 +8404,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8421,16 +8430,16 @@
         <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8480,7 +8489,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8509,10 +8518,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8535,13 +8544,13 @@
         <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8592,7 +8601,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8601,7 +8610,7 @@
         <v>87</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>99</v>
@@ -8624,7 +8633,7 @@
         <v>288</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8647,13 +8656,13 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8704,25 +8713,25 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL63" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
@@ -8736,11 +8745,11 @@
         <v>289</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8759,16 +8768,16 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8818,7 +8827,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -8830,13 +8839,13 @@
         <v>77</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
@@ -8850,11 +8859,11 @@
         <v>290</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8873,19 +8882,19 @@
         <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O65" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -8934,7 +8943,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -8946,7 +8955,7 @@
         <v>77</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>77</v>
@@ -8966,7 +8975,7 @@
         <v>291</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8992,10 +9001,10 @@
         <v>107</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9007,29 +9016,29 @@
         <v>77</v>
       </c>
       <c r="S66" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="Z66" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="T66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>226</v>
-      </c>
       <c r="AA66" t="s" s="2">
         <v>77</v>
       </c>
@@ -9046,7 +9055,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>87</v>
@@ -9078,7 +9087,7 @@
         <v>292</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9104,13 +9113,13 @@
         <v>101</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9160,7 +9169,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>87</v>
@@ -9192,7 +9201,7 @@
         <v>293</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9215,13 +9224,13 @@
         <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9272,7 +9281,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9304,7 +9313,7 @@
         <v>294</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9327,13 +9336,13 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9384,7 +9393,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9416,7 +9425,7 @@
         <v>295</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9439,13 +9448,13 @@
         <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9496,7 +9505,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9528,7 +9537,7 @@
         <v>296</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9551,13 +9560,13 @@
         <v>88</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9608,7 +9617,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9640,7 +9649,7 @@
         <v>297</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9663,13 +9672,13 @@
         <v>88</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9720,7 +9729,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -9729,7 +9738,7 @@
         <v>87</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>99</v>
@@ -9752,7 +9761,7 @@
         <v>298</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9775,13 +9784,13 @@
         <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9832,25 +9841,25 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL73" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
@@ -9864,11 +9873,11 @@
         <v>299</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -9887,16 +9896,16 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9946,7 +9955,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -9958,13 +9967,13 @@
         <v>77</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
@@ -9978,11 +9987,11 @@
         <v>300</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10001,19 +10010,19 @@
         <v>88</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O75" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>77</v>
@@ -10062,7 +10071,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10074,7 +10083,7 @@
         <v>77</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>77</v>
@@ -10094,7 +10103,7 @@
         <v>301</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10117,13 +10126,13 @@
         <v>88</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10174,7 +10183,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>87</v>
@@ -10206,7 +10215,7 @@
         <v>302</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10232,10 +10241,10 @@
         <v>101</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10286,7 +10295,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10318,7 +10327,7 @@
         <v>303</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10341,16 +10350,16 @@
         <v>88</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="N78" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10400,7 +10409,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10432,7 +10441,7 @@
         <v>304</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10455,16 +10464,16 @@
         <v>88</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N79" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10514,7 +10523,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -10546,7 +10555,7 @@
         <v>305</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10569,16 +10578,16 @@
         <v>88</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N80" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -10628,7 +10637,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -10660,7 +10669,7 @@
         <v>306</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C81" t="s" s="2">
         <v>307</v>
@@ -10685,13 +10694,13 @@
         <v>88</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L81" t="s" s="2">
         <v>308</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10742,7 +10751,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -10754,7 +10763,7 @@
         <v>77</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>77</v>
@@ -10774,7 +10783,7 @@
         <v>309</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10797,13 +10806,13 @@
         <v>77</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="M82" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -10854,25 +10863,25 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL82" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>77</v>
@@ -10886,11 +10895,11 @@
         <v>310</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -10909,16 +10918,16 @@
         <v>77</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L83" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="M83" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -10968,7 +10977,7 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -10980,13 +10989,13 @@
         <v>77</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>77</v>
@@ -11000,11 +11009,11 @@
         <v>311</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -11023,19 +11032,19 @@
         <v>88</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O84" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>77</v>
@@ -11084,7 +11093,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11096,7 +11105,7 @@
         <v>77</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>77</v>
@@ -11116,7 +11125,7 @@
         <v>312</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11142,10 +11151,10 @@
         <v>80</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11196,7 +11205,7 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -11228,7 +11237,7 @@
         <v>313</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11254,13 +11263,13 @@
         <v>101</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11310,7 +11319,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -11342,7 +11351,7 @@
         <v>314</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11422,7 +11431,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -11454,7 +11463,7 @@
         <v>320</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11477,13 +11486,13 @@
         <v>88</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -11534,7 +11543,7 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -11543,7 +11552,7 @@
         <v>87</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>99</v>
@@ -11566,7 +11575,7 @@
         <v>321</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11589,13 +11598,13 @@
         <v>77</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="M89" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -11646,25 +11655,25 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL89" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>77</v>
@@ -11678,11 +11687,11 @@
         <v>322</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -11701,16 +11710,16 @@
         <v>77</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L90" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L90" t="s" s="2">
+      <c r="M90" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -11760,7 +11769,7 @@
         <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -11772,13 +11781,13 @@
         <v>77</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>77</v>
@@ -11792,11 +11801,11 @@
         <v>323</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -11815,19 +11824,19 @@
         <v>88</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O91" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>77</v>
@@ -11876,7 +11885,7 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -11888,7 +11897,7 @@
         <v>77</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>77</v>
@@ -11908,7 +11917,7 @@
         <v>324</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11934,13 +11943,13 @@
         <v>107</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -11966,14 +11975,14 @@
         <v>77</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Y92" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="Z92" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="Z92" t="s" s="2">
-        <v>208</v>
-      </c>
       <c r="AA92" t="s" s="2">
         <v>77</v>
       </c>
@@ -11990,7 +11999,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -12022,7 +12031,7 @@
         <v>325</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12045,16 +12054,16 @@
         <v>88</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L93" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="M93" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12104,7 +12113,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -12136,7 +12145,7 @@
         <v>326</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12159,13 +12168,13 @@
         <v>88</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -12216,7 +12225,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -12225,7 +12234,7 @@
         <v>87</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>99</v>
@@ -12245,10 +12254,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12271,13 +12280,13 @@
         <v>77</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -12328,25 +12337,25 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL95" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH95" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI95" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ95" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK95" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>77</v>
@@ -12357,14 +12366,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -12383,16 +12392,16 @@
         <v>77</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L96" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="M96" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -12442,7 +12451,7 @@
         <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -12454,13 +12463,13 @@
         <v>77</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>77</v>
@@ -12471,14 +12480,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -12497,19 +12506,19 @@
         <v>88</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O97" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>77</v>
@@ -12558,7 +12567,7 @@
         <v>77</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -12570,7 +12579,7 @@
         <v>77</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>77</v>
@@ -12587,10 +12596,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12616,10 +12625,10 @@
         <v>107</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -12631,29 +12640,29 @@
         <v>77</v>
       </c>
       <c r="S98" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="Z98" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="T98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X98" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="Z98" t="s" s="2">
-        <v>226</v>
-      </c>
       <c r="AA98" t="s" s="2">
         <v>77</v>
       </c>
@@ -12670,7 +12679,7 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>87</v>
@@ -12699,10 +12708,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12728,13 +12737,13 @@
         <v>101</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="N99" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -12784,7 +12793,7 @@
         <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>87</v>
@@ -12813,10 +12822,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12839,13 +12848,13 @@
         <v>88</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -12896,7 +12905,7 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -12925,10 +12934,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12951,13 +12960,13 @@
         <v>88</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -13008,7 +13017,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -13037,10 +13046,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13063,13 +13072,13 @@
         <v>88</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -13120,7 +13129,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -13149,10 +13158,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13175,13 +13184,13 @@
         <v>88</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -13232,7 +13241,7 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -13261,10 +13270,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13287,13 +13296,13 @@
         <v>88</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -13344,7 +13353,7 @@
         <v>77</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -13353,7 +13362,7 @@
         <v>87</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>99</v>
@@ -13373,10 +13382,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13399,13 +13408,13 @@
         <v>77</v>
       </c>
       <c r="K105" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L105" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L105" t="s" s="2">
+      <c r="M105" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -13456,25 +13465,25 @@
         <v>77</v>
       </c>
       <c r="AF105" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL105" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH105" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>77</v>
@@ -13485,14 +13494,14 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -13511,16 +13520,16 @@
         <v>77</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L106" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L106" t="s" s="2">
+      <c r="M106" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M106" t="s" s="2">
+      <c r="N106" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -13570,7 +13579,7 @@
         <v>77</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -13582,13 +13591,13 @@
         <v>77</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>77</v>
@@ -13599,14 +13608,14 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -13625,19 +13634,19 @@
         <v>88</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O107" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>77</v>
@@ -13686,7 +13695,7 @@
         <v>77</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -13698,7 +13707,7 @@
         <v>77</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>77</v>
@@ -13715,10 +13724,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13741,13 +13750,13 @@
         <v>88</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -13798,7 +13807,7 @@
         <v>77</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>87</v>
@@ -13827,10 +13836,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13856,10 +13865,10 @@
         <v>101</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -13910,7 +13919,7 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -13939,10 +13948,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13965,16 +13974,16 @@
         <v>88</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="N110" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -14024,7 +14033,7 @@
         <v>77</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -14053,10 +14062,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14079,16 +14088,16 @@
         <v>88</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N111" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14138,7 +14147,7 @@
         <v>77</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -14167,10 +14176,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14193,16 +14202,16 @@
         <v>88</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N112" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -14252,7 +14261,7 @@
         <v>77</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -14281,13 +14290,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>77</v>
@@ -14309,13 +14318,13 @@
         <v>88</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -14366,7 +14375,7 @@
         <v>77</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -14378,7 +14387,7 @@
         <v>77</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>77</v>
@@ -14395,10 +14404,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14421,13 +14430,13 @@
         <v>77</v>
       </c>
       <c r="K114" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L114" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L114" t="s" s="2">
+      <c r="M114" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -14478,25 +14487,25 @@
         <v>77</v>
       </c>
       <c r="AF114" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL114" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH114" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL114" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>77</v>
@@ -14507,14 +14516,14 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -14533,16 +14542,16 @@
         <v>77</v>
       </c>
       <c r="K115" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L115" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L115" t="s" s="2">
+      <c r="M115" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -14592,7 +14601,7 @@
         <v>77</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -14604,13 +14613,13 @@
         <v>77</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>77</v>
@@ -14621,14 +14630,14 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -14647,19 +14656,19 @@
         <v>88</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M116" t="s" s="2">
+      <c r="N116" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O116" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>77</v>
@@ -14708,7 +14717,7 @@
         <v>77</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -14720,7 +14729,7 @@
         <v>77</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>77</v>
@@ -14737,10 +14746,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14766,10 +14775,10 @@
         <v>80</v>
       </c>
       <c r="L117" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M117" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -14820,7 +14829,7 @@
         <v>77</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
@@ -14849,10 +14858,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14878,13 +14887,13 @@
         <v>101</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M118" t="s" s="2">
+      <c r="N118" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -14934,7 +14943,7 @@
         <v>77</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
@@ -14963,10 +14972,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14989,13 +14998,13 @@
         <v>77</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -15046,7 +15055,7 @@
         <v>77</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
@@ -15061,10 +15070,10 @@
         <v>77</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>77</v>
@@ -15075,10 +15084,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15101,13 +15110,13 @@
         <v>88</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -15158,7 +15167,7 @@
         <v>77</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -15167,7 +15176,7 @@
         <v>87</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AJ120" t="s" s="2">
         <v>99</v>
@@ -15187,10 +15196,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15213,13 +15222,13 @@
         <v>77</v>
       </c>
       <c r="K121" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L121" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L121" t="s" s="2">
+      <c r="M121" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -15270,25 +15279,25 @@
         <v>77</v>
       </c>
       <c r="AF121" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL121" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH121" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL121" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>77</v>
@@ -15299,14 +15308,14 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -15325,16 +15334,16 @@
         <v>77</v>
       </c>
       <c r="K122" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L122" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L122" t="s" s="2">
+      <c r="M122" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M122" t="s" s="2">
+      <c r="N122" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -15384,7 +15393,7 @@
         <v>77</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -15396,13 +15405,13 @@
         <v>77</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>77</v>
@@ -15413,14 +15422,14 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
@@ -15439,19 +15448,19 @@
         <v>88</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="N123" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O123" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>77</v>
@@ -15500,7 +15509,7 @@
         <v>77</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -15512,7 +15521,7 @@
         <v>77</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>77</v>
@@ -15529,10 +15538,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15558,13 +15567,13 @@
         <v>107</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M124" t="s" s="2">
+      <c r="N124" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -15590,14 +15599,14 @@
         <v>77</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Y124" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="Z124" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="Z124" t="s" s="2">
-        <v>208</v>
-      </c>
       <c r="AA124" t="s" s="2">
         <v>77</v>
       </c>
@@ -15614,7 +15623,7 @@
         <v>77</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -15643,10 +15652,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15669,16 +15678,16 @@
         <v>88</v>
       </c>
       <c r="K125" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L125" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L125" t="s" s="2">
+      <c r="M125" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="M125" t="s" s="2">
+      <c r="N125" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -15728,7 +15737,7 @@
         <v>77</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -15757,10 +15766,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15783,13 +15792,13 @@
         <v>88</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -15840,7 +15849,7 @@
         <v>77</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -15849,7 +15858,7 @@
         <v>87</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>99</v>
@@ -15869,10 +15878,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15895,13 +15904,13 @@
         <v>77</v>
       </c>
       <c r="K127" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L127" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L127" t="s" s="2">
+      <c r="M127" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -15952,25 +15961,25 @@
         <v>77</v>
       </c>
       <c r="AF127" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL127" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH127" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL127" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>77</v>
@@ -15981,14 +15990,14 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -16007,16 +16016,16 @@
         <v>77</v>
       </c>
       <c r="K128" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L128" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L128" t="s" s="2">
+      <c r="M128" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M128" t="s" s="2">
+      <c r="N128" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -16066,7 +16075,7 @@
         <v>77</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
@@ -16078,13 +16087,13 @@
         <v>77</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>77</v>
@@ -16095,14 +16104,14 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
@@ -16121,19 +16130,19 @@
         <v>88</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L129" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M129" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M129" t="s" s="2">
+      <c r="N129" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O129" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O129" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>77</v>
@@ -16182,7 +16191,7 @@
         <v>77</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>78</v>
@@ -16194,7 +16203,7 @@
         <v>77</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>77</v>
@@ -16211,10 +16220,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -16240,10 +16249,10 @@
         <v>107</v>
       </c>
       <c r="L130" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M130" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -16255,29 +16264,29 @@
         <v>77</v>
       </c>
       <c r="S130" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="Z130" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="T130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X130" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="Y130" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="Z130" t="s" s="2">
-        <v>226</v>
-      </c>
       <c r="AA130" t="s" s="2">
         <v>77</v>
       </c>
@@ -16294,7 +16303,7 @@
         <v>77</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>87</v>
@@ -16323,10 +16332,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -16352,13 +16361,13 @@
         <v>101</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="N131" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -16408,7 +16417,7 @@
         <v>77</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>87</v>
@@ -16437,10 +16446,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -16463,13 +16472,13 @@
         <v>88</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -16520,7 +16529,7 @@
         <v>77</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>78</v>
@@ -16549,10 +16558,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -16575,13 +16584,13 @@
         <v>88</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -16632,7 +16641,7 @@
         <v>77</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>78</v>
@@ -16661,10 +16670,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -16687,13 +16696,13 @@
         <v>88</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -16744,7 +16753,7 @@
         <v>77</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>78</v>
@@ -16773,10 +16782,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16799,13 +16808,13 @@
         <v>88</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -16856,7 +16865,7 @@
         <v>77</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -16885,10 +16894,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -16911,13 +16920,13 @@
         <v>88</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -16968,7 +16977,7 @@
         <v>77</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>78</v>
@@ -16977,7 +16986,7 @@
         <v>87</v>
       </c>
       <c r="AI136" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AJ136" t="s" s="2">
         <v>99</v>
@@ -16997,10 +17006,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17023,13 +17032,13 @@
         <v>77</v>
       </c>
       <c r="K137" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L137" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L137" t="s" s="2">
+      <c r="M137" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="M137" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -17080,25 +17089,25 @@
         <v>77</v>
       </c>
       <c r="AF137" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH137" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI137" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ137" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK137" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL137" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AG137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH137" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI137" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ137" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK137" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL137" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>77</v>
@@ -17109,14 +17118,14 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -17135,16 +17144,16 @@
         <v>77</v>
       </c>
       <c r="K138" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L138" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L138" t="s" s="2">
+      <c r="M138" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M138" t="s" s="2">
+      <c r="N138" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -17194,7 +17203,7 @@
         <v>77</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>78</v>
@@ -17206,13 +17215,13 @@
         <v>77</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM138" t="s" s="2">
         <v>77</v>
@@ -17223,14 +17232,14 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
@@ -17249,19 +17258,19 @@
         <v>88</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L139" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M139" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M139" t="s" s="2">
+      <c r="N139" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O139" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O139" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>77</v>
@@ -17310,7 +17319,7 @@
         <v>77</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>78</v>
@@ -17322,7 +17331,7 @@
         <v>77</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AK139" t="s" s="2">
         <v>77</v>
@@ -17339,10 +17348,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -17365,13 +17374,13 @@
         <v>88</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -17422,7 +17431,7 @@
         <v>77</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>87</v>
@@ -17451,10 +17460,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -17480,10 +17489,10 @@
         <v>101</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -17534,7 +17543,7 @@
         <v>77</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>78</v>
@@ -17563,10 +17572,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -17589,16 +17598,16 @@
         <v>88</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L142" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M142" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="N142" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -17648,7 +17657,7 @@
         <v>77</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>78</v>
@@ -17677,10 +17686,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -17703,16 +17712,16 @@
         <v>88</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L143" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M143" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N143" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="M143" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -17762,7 +17771,7 @@
         <v>77</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>78</v>
@@ -17791,10 +17800,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -17817,16 +17826,16 @@
         <v>88</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L144" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M144" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N144" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="M144" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -17876,7 +17885,7 @@
         <v>77</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>78</v>
@@ -17905,10 +17914,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -17931,19 +17940,19 @@
         <v>88</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>77</v>
@@ -17992,7 +18001,7 @@
         <v>77</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>78</v>

--- a/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-bundle-urgencia.xlsx
+++ b/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-bundle-urgencia.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5208" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5208" uniqueCount="393">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:47:41-03:00</t>
+    <t>2026-10-08T00:02:21-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,7 +269,7 @@
   </si>
   <si>
     <t>bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}
-bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}urg-tx-put-condicional:Todas las entradas deben usar PUT condicional por identificador: request.method = PUT y request.url = [Tipo]?identifier=[system]|[value]. {entry.all(request.method = 'PUT' and request.url.contains('?identifier=') and request.url.contains('|'))}</t>
+bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}urg-tx-maestros:Patient, Organization y Practitioner se envían solo con creación condicional: request.method = POST, request.url = [Tipo] y request.ifNoneExist = identifier=[system]|[value]. Nunca se actualizan. {entry.where(resource is Patient or resource is Organization or resource is Practitioner).all(request.method = 'POST' and request.ifNoneExist.startsWith('identifier=') and request.ifNoneExist.contains('|'))}urg-tx-put-condicional:Los recursos del episodio (Encounter, Condition, MedicationRequest, DocumentReference) se envían con PUT condicional: request.method = PUT y request.url = [Tipo]?identifier=[system]|[value]. {entry.where((resource is Patient or resource is Organization or resource is Practitioner).not()).all(request.method = 'PUT' and request.url.contains('?identifier=') and request.url.contains('|'))}urg-tx-sin-id:Los recursos enviados con PUT condicional no llevan Resource.id: el id lo determina el servidor al encontrar (o crear) el recurso por su identificador. {entry.where(request.method = 'PUT').all(resource.id.empty())}urg-tx-identificador:El identificador de la operación condicional (request.url o request.ifNoneExist) debe ser el mismo que trae el recurso (identifier o masterIdentifier). {entry.where(request.method = 'PUT').select(request.url.substring(request.url.indexOf('|') + 1) in (resource.identifier.value | resource.masterIdentifier.value)).allTrue() and entry.where(request.method = 'POST').select(request.ifNoneExist.substring(request.ifNoneExist.indexOf('|') + 1) in resource.identifier.value).allTrue()}urg-tx-mismo-paciente:Todos los recursos del Bundle se refieren al mismo paciente: su subject apunta a la entrada del paciente. {(entry.resource.ofType(Encounter) | entry.resource.ofType(Condition) | entry.resource.ofType(MedicationRequest) | entry.resource.ofType(DocumentReference)).all(subject.reference = %resource.entry.where(resource is Patient).fullUrl.first())}urg-tx-restringido:Si el episodio está marcado como restringido (meta.security = R), también deben estarlo sus diagnósticos, indicaciones y documento. {entry.resource.ofType(Encounter).meta.security.where(code = 'R').exists() implies (entry.resource.ofType(Condition) | entry.resource.ofType(MedicationRequest) | entry.resource.ofType(DocumentReference)).all(meta.security.where(system = 'http://terminology.hl7.org/CodeSystem/v3-Confidentiality' and code = 'R').exists())}</t>
   </si>
   <si>
     <t>N/A</t>
@@ -573,7 +573,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Entrada: recurso más su PUT condicional</t>
+    <t>Entrada: recurso más su operación condicional</t>
   </si>
   <si>
     <t>An entry in a bundle resource - will either contain a resource or information about a resource (transactions and history only).</t>
@@ -696,7 +696,7 @@
     <t>Bundle.entry.request</t>
   </si>
   <si>
-    <t>Operación: PUT condicional por identificador</t>
+    <t>POST con ifNoneExist (maestros) o PUT condicional (episodio)</t>
   </si>
   <si>
     <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
@@ -718,7 +718,7 @@
     <t>Bundle.entry.request.method</t>
   </si>
   <si>
-    <t>PUT</t>
+    <t>POST (maestros) | PUT (episodio)</t>
   </si>
   <si>
     <t>In a transaction or batch, this is the HTTP action to be executed for this entry. In a history bundle, this indicates the HTTP action that occurred.</t>
@@ -733,7 +733,7 @@
     <t>Bundle.entry.request.url</t>
   </si>
   <si>
-    <t>[Tipo]?identifier=[system]|[value]</t>
+    <t>[Tipo] (maestros) o [Tipo]?identifier=[sistema]|[valor] (episodio)</t>
   </si>
   <si>
     <t>The URL for this entry, relative to the root (the address to which the request is posted).</t>
@@ -769,7 +769,7 @@
     <t>Bundle.entry.request.ifNoneExist</t>
   </si>
   <si>
-    <t>For conditional creates</t>
+    <t>identifier=[sistema]|[valor] (solo maestros)</t>
   </si>
   <si>
     <t>Instruct the server not to perform the create if a specified resource already exists. For further information, see the API documentation for ["Conditional Create"](http://hl7.org/fhir/R4/http.html#ccreate). This is just the query portion of the URL - what follows the "?" (not including the "?").</t>
@@ -920,7 +920,7 @@
     <t>Bundle.entry:paciente.request</t>
   </si>
   <si>
-    <t>PUT Patient?identifier=[sistema]|[valor]</t>
+    <t>POST Patient, ifNoneExist identifier=[sistema]|[valor]</t>
   </si>
   <si>
     <t>Bundle.entry:paciente.request.id</t>
@@ -933,6 +933,9 @@
   </si>
   <si>
     <t>Bundle.entry:paciente.request.method</t>
+  </si>
+  <si>
+    <t>POST</t>
   </si>
   <si>
     <t>Bundle.entry:paciente.request.url</t>
@@ -1041,7 +1044,7 @@
     <t>Bundle.entry:establecimiento.request</t>
   </si>
   <si>
-    <t>PUT Organization?identifier=[sistema DEIS]|[código]</t>
+    <t>POST Organization, ifNoneExist identifier=[sistema DEIS]|[código]</t>
   </si>
   <si>
     <t>Bundle.entry:establecimiento.request.id</t>
@@ -1162,7 +1165,7 @@
     <t>Bundle.entry:profesional.request</t>
   </si>
   <si>
-    <t>PUT Practitioner?identifier=[sistema]|[RUN]</t>
+    <t>POST Practitioner, ifNoneExist identifier=[sistema]|[RUN]</t>
   </si>
   <si>
     <t>Bundle.entry:profesional.request.id</t>
@@ -5392,7 +5395,7 @@
         <v>77</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>221</v>
+        <v>77</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>77</v>
@@ -9016,7 +9019,7 @@
         <v>77</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>221</v>
+        <v>292</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>77</v>
@@ -9084,7 +9087,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>225</v>
@@ -9198,7 +9201,7 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>229</v>
@@ -9310,7 +9313,7 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>232</v>
@@ -9422,7 +9425,7 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>234</v>
@@ -9534,7 +9537,7 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>237</v>
@@ -9545,7 +9548,7 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>87</v>
@@ -9646,7 +9649,7 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>240</v>
@@ -9758,7 +9761,7 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>244</v>
@@ -9870,7 +9873,7 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>245</v>
@@ -9984,7 +9987,7 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>246</v>
@@ -10100,7 +10103,7 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>247</v>
@@ -10212,7 +10215,7 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>250</v>
@@ -10324,7 +10327,7 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>253</v>
@@ -10438,7 +10441,7 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>257</v>
@@ -10552,7 +10555,7 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>261</v>
@@ -10666,13 +10669,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>174</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>77</v>
@@ -10697,7 +10700,7 @@
         <v>144</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M81" t="s" s="2">
         <v>177</v>
@@ -10780,7 +10783,7 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>181</v>
@@ -10892,7 +10895,7 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>182</v>
@@ -11006,7 +11009,7 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>183</v>
@@ -11122,7 +11125,7 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>184</v>
@@ -11234,7 +11237,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>187</v>
@@ -11348,7 +11351,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>191</v>
@@ -11374,13 +11377,13 @@
         <v>77</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -11446,10 +11449,10 @@
         <v>77</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>77</v>
@@ -11460,7 +11463,7 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>195</v>
@@ -11572,7 +11575,7 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>199</v>
@@ -11684,7 +11687,7 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>200</v>
@@ -11798,7 +11801,7 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>201</v>
@@ -11914,7 +11917,7 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>202</v>
@@ -12028,7 +12031,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>208</v>
@@ -12142,7 +12145,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>213</v>
@@ -12171,7 +12174,7 @@
         <v>144</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M94" t="s" s="2">
         <v>215</v>
@@ -12254,7 +12257,7 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>217</v>
@@ -12366,7 +12369,7 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>218</v>
@@ -12480,7 +12483,7 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>219</v>
@@ -12596,7 +12599,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>220</v>
@@ -12640,7 +12643,7 @@
         <v>77</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>221</v>
+        <v>292</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>77</v>
@@ -12708,7 +12711,7 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>225</v>
@@ -12822,7 +12825,7 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>229</v>
@@ -12934,7 +12937,7 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>232</v>
@@ -13046,7 +13049,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>234</v>
@@ -13158,7 +13161,7 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>237</v>
@@ -13169,7 +13172,7 @@
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>87</v>
@@ -13270,7 +13273,7 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>240</v>
@@ -13382,7 +13385,7 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>244</v>
@@ -13494,7 +13497,7 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>245</v>
@@ -13608,7 +13611,7 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>246</v>
@@ -13724,7 +13727,7 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>247</v>
@@ -13836,7 +13839,7 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>250</v>
@@ -13948,7 +13951,7 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>253</v>
@@ -14062,7 +14065,7 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>257</v>
@@ -14176,7 +14179,7 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>261</v>
@@ -14290,13 +14293,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>174</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>77</v>
@@ -14321,7 +14324,7 @@
         <v>144</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M113" t="s" s="2">
         <v>177</v>
@@ -14404,7 +14407,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>181</v>
@@ -14516,7 +14519,7 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>182</v>
@@ -14630,7 +14633,7 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>183</v>
@@ -14746,7 +14749,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>184</v>
@@ -14858,7 +14861,7 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>187</v>
@@ -14972,7 +14975,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>191</v>
@@ -14998,13 +15001,13 @@
         <v>77</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -15070,10 +15073,10 @@
         <v>77</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>77</v>
@@ -15084,7 +15087,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>195</v>
@@ -15196,7 +15199,7 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>199</v>
@@ -15308,7 +15311,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>200</v>
@@ -15422,7 +15425,7 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>201</v>
@@ -15538,7 +15541,7 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>202</v>
@@ -15652,7 +15655,7 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>208</v>
@@ -15766,7 +15769,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>213</v>
@@ -15795,7 +15798,7 @@
         <v>144</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M126" t="s" s="2">
         <v>215</v>
@@ -15878,7 +15881,7 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>217</v>
@@ -15990,7 +15993,7 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>218</v>
@@ -16104,7 +16107,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>219</v>
@@ -16220,7 +16223,7 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>220</v>
@@ -16264,7 +16267,7 @@
         <v>77</v>
       </c>
       <c r="S130" t="s" s="2">
-        <v>221</v>
+        <v>292</v>
       </c>
       <c r="T130" t="s" s="2">
         <v>77</v>
@@ -16332,7 +16335,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>225</v>
@@ -16446,7 +16449,7 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>229</v>
@@ -16558,7 +16561,7 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>232</v>
@@ -16670,7 +16673,7 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>234</v>
@@ -16782,7 +16785,7 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>237</v>
@@ -16793,7 +16796,7 @@
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G135" t="s" s="2">
         <v>87</v>
@@ -16894,7 +16897,7 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>240</v>
@@ -17006,7 +17009,7 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>244</v>
@@ -17118,7 +17121,7 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>245</v>
@@ -17232,7 +17235,7 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>246</v>
@@ -17348,7 +17351,7 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>247</v>
@@ -17460,7 +17463,7 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>250</v>
@@ -17572,7 +17575,7 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>253</v>
@@ -17686,7 +17689,7 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>257</v>
@@ -17800,7 +17803,7 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>261</v>
@@ -17914,10 +17917,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -17940,19 +17943,19 @@
         <v>88</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>77</v>
@@ -18001,7 +18004,7 @@
         <v>77</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>78</v>
